--- a/Data/EXCEL/Transfer/salemon/202208/8932-salemon-202208.xlsx
+++ b/Data/EXCEL/Transfer/salemon/202208/8932-salemon-202208.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WORKSPACES\GoodinfoWebData\salemon\202208\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\WORKSPACES\xls2xlsx\Transfer\202208\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{ACF40282-5A1A-4A8B-9908-7E3E12AA0151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B0146083-3C3F-4DFE-9EB3-D910DA038644}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3510" yWindow="1395" windowWidth="22035" windowHeight="12855"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="30645" windowHeight="19905"/>
   </bookViews>
   <sheets>
     <sheet name="8932-salemon-202208" sheetId="2" r:id="rId1"/>
@@ -80,7 +80,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="25">
+  <fonts count="26" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -246,7 +246,7 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="新細明體"/>
-      <family val="2"/>
+      <family val="1"/>
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
@@ -263,7 +263,7 @@
       <sz val="10"/>
       <color rgb="FFFF0000"/>
       <name val="新細明體"/>
-      <family val="2"/>
+      <family val="1"/>
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
@@ -271,13 +271,21 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="新細明體"/>
-      <family val="2"/>
+      <family val="1"/>
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF008000"/>
+      <name val="新細明體"/>
+      <family val="1"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
       <name val="新細明體"/>
       <family val="2"/>
       <charset val="136"/>
@@ -818,7 +826,7 @@
     <xf numFmtId="0" fontId="18" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -827,7 +835,7 @@
     <xf numFmtId="0" fontId="20" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="17" fontId="19" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -845,22 +853,22 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1219,17 +1227,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:Q299"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.25" customWidth="1"/>
-    <col min="2" max="5" width="9.5" customWidth="1"/>
-    <col min="6" max="6" width="10.5" customWidth="1"/>
-    <col min="7" max="7" width="11" customWidth="1"/>
-    <col min="8" max="16" width="9.5" customWidth="1"/>
-    <col min="17" max="17" width="11" customWidth="1"/>
+    <col min="1" max="1" width="16.625" customWidth="1"/>
+    <col min="2" max="5" width="14" customWidth="1"/>
+    <col min="6" max="6" width="15.25" customWidth="1"/>
+    <col min="7" max="7" width="16" customWidth="1"/>
+    <col min="8" max="16" width="14" customWidth="1"/>
+    <col min="17" max="17" width="14.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="1" customFormat="1" ht="16.5" customHeight="1">
+    <row r="1" spans="1:17" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
@@ -1256,7 +1264,7 @@
       <c r="P1" s="15"/>
       <c r="Q1" s="16"/>
     </row>
-    <row r="2" spans="1:17" s="1" customFormat="1" ht="16.5" customHeight="1">
+    <row r="2" spans="1:17" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="12"/>
       <c r="B2" s="11" t="s">
         <v>4</v>
@@ -1295,7 +1303,7 @@
       </c>
       <c r="Q2" s="16"/>
     </row>
-    <row r="3" spans="1:17" s="1" customFormat="1">
+    <row r="3" spans="1:17" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="12"/>
       <c r="B3" s="12"/>
       <c r="C3" s="12"/>
@@ -1338,7 +1346,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:17" s="1" customFormat="1">
+    <row r="4" spans="1:17" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="13"/>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -1377,7 +1385,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:17" s="5" customFormat="1">
+    <row r="5" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="6">
         <v>44774</v>
       </c>
@@ -1430,7 +1438,7 @@
         <v>-4.75</v>
       </c>
     </row>
-    <row r="6" spans="1:17" s="5" customFormat="1">
+    <row r="6" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="6">
         <v>44743</v>
       </c>
@@ -1483,7 +1491,7 @@
         <v>-4.63</v>
       </c>
     </row>
-    <row r="7" spans="1:17" s="5" customFormat="1">
+    <row r="7" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="6">
         <v>44713</v>
       </c>
@@ -1536,7 +1544,7 @@
         <v>-0.16</v>
       </c>
     </row>
-    <row r="8" spans="1:17" s="5" customFormat="1">
+    <row r="8" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="6">
         <v>44682</v>
       </c>
@@ -1589,7 +1597,7 @@
         <v>2.74</v>
       </c>
     </row>
-    <row r="9" spans="1:17" s="5" customFormat="1">
+    <row r="9" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="6">
         <v>44652</v>
       </c>
@@ -1642,7 +1650,7 @@
         <v>8.6</v>
       </c>
     </row>
-    <row r="10" spans="1:17" s="5" customFormat="1">
+    <row r="10" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="6">
         <v>44621</v>
       </c>
@@ -1695,7 +1703,7 @@
         <v>35.5</v>
       </c>
     </row>
-    <row r="11" spans="1:17" s="5" customFormat="1">
+    <row r="11" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="6">
         <v>44593</v>
       </c>
@@ -1748,7 +1756,7 @@
         <v>68.599999999999994</v>
       </c>
     </row>
-    <row r="12" spans="1:17" s="5" customFormat="1">
+    <row r="12" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="6">
         <v>44562</v>
       </c>
@@ -1801,7 +1809,7 @@
         <v>102.2</v>
       </c>
     </row>
-    <row r="13" spans="1:17" s="5" customFormat="1">
+    <row r="13" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="6">
         <v>44531</v>
       </c>
@@ -1854,7 +1862,7 @@
         <v>18.399999999999999</v>
       </c>
     </row>
-    <row r="14" spans="1:17" s="5" customFormat="1">
+    <row r="14" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="6">
         <v>44501</v>
       </c>
@@ -1907,7 +1915,7 @@
         <v>14.6</v>
       </c>
     </row>
-    <row r="15" spans="1:17" s="5" customFormat="1">
+    <row r="15" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="6">
         <v>44470</v>
       </c>
@@ -1960,7 +1968,7 @@
         <v>13.9</v>
       </c>
     </row>
-    <row r="16" spans="1:17" s="5" customFormat="1">
+    <row r="16" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="6">
         <v>44440</v>
       </c>
@@ -2013,7 +2021,7 @@
         <v>16.399999999999999</v>
       </c>
     </row>
-    <row r="17" spans="1:17" s="5" customFormat="1">
+    <row r="17" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="6">
         <v>44409</v>
       </c>
@@ -2066,7 +2074,7 @@
         <v>19.8</v>
       </c>
     </row>
-    <row r="18" spans="1:17" s="5" customFormat="1">
+    <row r="18" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="6">
         <v>44378</v>
       </c>
@@ -2119,7 +2127,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="19" spans="1:17" s="5" customFormat="1">
+    <row r="19" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="6">
         <v>44348</v>
       </c>
@@ -2172,7 +2180,7 @@
         <v>30.6</v>
       </c>
     </row>
-    <row r="20" spans="1:17" s="5" customFormat="1">
+    <row r="20" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="6">
         <v>44317</v>
       </c>
@@ -2225,7 +2233,7 @@
         <v>21.6</v>
       </c>
     </row>
-    <row r="21" spans="1:17" s="5" customFormat="1">
+    <row r="21" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="6">
         <v>44287</v>
       </c>
@@ -2278,7 +2286,7 @@
         <v>22.8</v>
       </c>
     </row>
-    <row r="22" spans="1:17" s="5" customFormat="1">
+    <row r="22" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="6">
         <v>44256</v>
       </c>
@@ -2331,7 +2339,7 @@
         <v>24.9</v>
       </c>
     </row>
-    <row r="23" spans="1:17" s="5" customFormat="1">
+    <row r="23" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="6">
         <v>44228</v>
       </c>
@@ -2384,7 +2392,7 @@
         <v>20.3</v>
       </c>
     </row>
-    <row r="24" spans="1:17" s="5" customFormat="1">
+    <row r="24" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="6">
         <v>44197</v>
       </c>
@@ -2437,7 +2445,7 @@
         <v>44.2</v>
       </c>
     </row>
-    <row r="25" spans="1:17" s="5" customFormat="1">
+    <row r="25" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="6">
         <v>44166</v>
       </c>
@@ -2490,7 +2498,7 @@
         <v>-11.8</v>
       </c>
     </row>
-    <row r="26" spans="1:17" s="5" customFormat="1">
+    <row r="26" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="6">
         <v>44136</v>
       </c>
@@ -2543,7 +2551,7 @@
         <v>-11.2</v>
       </c>
     </row>
-    <row r="27" spans="1:17" s="5" customFormat="1">
+    <row r="27" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="6">
         <v>44105</v>
       </c>
@@ -2596,7 +2604,7 @@
         <v>-11.6</v>
       </c>
     </row>
-    <row r="28" spans="1:17" s="5" customFormat="1">
+    <row r="28" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="6">
         <v>44075</v>
       </c>
@@ -2649,7 +2657,7 @@
         <v>-11.6</v>
       </c>
     </row>
-    <row r="29" spans="1:17" s="5" customFormat="1">
+    <row r="29" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="6">
         <v>44044</v>
       </c>
@@ -2702,7 +2710,7 @@
         <v>-12.8</v>
       </c>
     </row>
-    <row r="30" spans="1:17" s="5" customFormat="1">
+    <row r="30" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="6">
         <v>44013</v>
       </c>
@@ -2755,7 +2763,7 @@
         <v>-13</v>
       </c>
     </row>
-    <row r="31" spans="1:17" s="5" customFormat="1">
+    <row r="31" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="6">
         <v>43983</v>
       </c>
@@ -2808,7 +2816,7 @@
         <v>-19.8</v>
       </c>
     </row>
-    <row r="32" spans="1:17" s="5" customFormat="1">
+    <row r="32" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="6">
         <v>43952</v>
       </c>
@@ -2861,7 +2869,7 @@
         <v>-18.2</v>
       </c>
     </row>
-    <row r="33" spans="1:17" s="5" customFormat="1">
+    <row r="33" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="6">
         <v>43922</v>
       </c>
@@ -2914,7 +2922,7 @@
         <v>-23.2</v>
       </c>
     </row>
-    <row r="34" spans="1:17" s="5" customFormat="1">
+    <row r="34" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="6">
         <v>43891</v>
       </c>
@@ -2967,7 +2975,7 @@
         <v>-27.1</v>
       </c>
     </row>
-    <row r="35" spans="1:17" s="5" customFormat="1">
+    <row r="35" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="6">
         <v>43862</v>
       </c>
@@ -3020,7 +3028,7 @@
         <v>-30</v>
       </c>
     </row>
-    <row r="36" spans="1:17" s="5" customFormat="1">
+    <row r="36" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="6">
         <v>43831</v>
       </c>
@@ -3073,7 +3081,7 @@
         <v>-44.2</v>
       </c>
     </row>
-    <row r="37" spans="1:17" s="5" customFormat="1">
+    <row r="37" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="6">
         <v>43800</v>
       </c>
@@ -3126,7 +3134,7 @@
         <v>-3.88</v>
       </c>
     </row>
-    <row r="38" spans="1:17" s="5" customFormat="1">
+    <row r="38" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A38" s="6">
         <v>43770</v>
       </c>
@@ -3179,7 +3187,7 @@
         <v>-4.25</v>
       </c>
     </row>
-    <row r="39" spans="1:17" s="5" customFormat="1">
+    <row r="39" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A39" s="6">
         <v>43739</v>
       </c>
@@ -3232,7 +3240,7 @@
         <v>-4.18</v>
       </c>
     </row>
-    <row r="40" spans="1:17" s="5" customFormat="1">
+    <row r="40" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A40" s="6">
         <v>43709</v>
       </c>
@@ -3285,7 +3293,7 @@
         <v>-4.9000000000000004</v>
       </c>
     </row>
-    <row r="41" spans="1:17" s="5" customFormat="1">
+    <row r="41" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A41" s="6">
         <v>43678</v>
       </c>
@@ -3338,7 +3346,7 @@
         <v>-6.29</v>
       </c>
     </row>
-    <row r="42" spans="1:17" s="5" customFormat="1">
+    <row r="42" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A42" s="6">
         <v>43647</v>
       </c>
@@ -3391,7 +3399,7 @@
         <v>-10.1</v>
       </c>
     </row>
-    <row r="43" spans="1:17" s="5" customFormat="1">
+    <row r="43" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A43" s="6">
         <v>43617</v>
       </c>
@@ -3444,7 +3452,7 @@
         <v>-10.6</v>
       </c>
     </row>
-    <row r="44" spans="1:17" s="5" customFormat="1">
+    <row r="44" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A44" s="6">
         <v>43586</v>
       </c>
@@ -3497,7 +3505,7 @@
         <v>-4.9800000000000004</v>
       </c>
     </row>
-    <row r="45" spans="1:17" s="5" customFormat="1">
+    <row r="45" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A45" s="6">
         <v>43556</v>
       </c>
@@ -3550,7 +3558,7 @@
         <v>-3.25</v>
       </c>
     </row>
-    <row r="46" spans="1:17" s="5" customFormat="1">
+    <row r="46" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A46" s="6">
         <v>43525</v>
       </c>
@@ -3603,7 +3611,7 @@
         <v>-1.44</v>
       </c>
     </row>
-    <row r="47" spans="1:17" s="5" customFormat="1">
+    <row r="47" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A47" s="6">
         <v>43497</v>
       </c>
@@ -3656,7 +3664,7 @@
         <v>10.9</v>
       </c>
     </row>
-    <row r="48" spans="1:17" s="5" customFormat="1">
+    <row r="48" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A48" s="6">
         <v>43466</v>
       </c>
@@ -3709,7 +3717,7 @@
         <v>15.8</v>
       </c>
     </row>
-    <row r="49" spans="1:17" s="5" customFormat="1">
+    <row r="49" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A49" s="6">
         <v>43435</v>
       </c>
@@ -3762,7 +3770,7 @@
         <v>-6.34</v>
       </c>
     </row>
-    <row r="50" spans="1:17" s="5" customFormat="1">
+    <row r="50" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A50" s="6">
         <v>43405</v>
       </c>
@@ -3815,7 +3823,7 @@
         <v>-4.1500000000000004</v>
       </c>
     </row>
-    <row r="51" spans="1:17" s="5" customFormat="1">
+    <row r="51" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A51" s="6">
         <v>43374</v>
       </c>
@@ -3868,7 +3876,7 @@
         <v>-4.29</v>
       </c>
     </row>
-    <row r="52" spans="1:17" s="5" customFormat="1">
+    <row r="52" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A52" s="6">
         <v>43344</v>
       </c>
@@ -3921,7 +3929,7 @@
         <v>-4.13</v>
       </c>
     </row>
-    <row r="53" spans="1:17" s="5" customFormat="1">
+    <row r="53" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A53" s="6">
         <v>43313</v>
       </c>
@@ -3974,7 +3982,7 @@
         <v>-3.97</v>
       </c>
     </row>
-    <row r="54" spans="1:17" s="5" customFormat="1">
+    <row r="54" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A54" s="6">
         <v>43282</v>
       </c>
@@ -4027,7 +4035,7 @@
         <v>-2.86</v>
       </c>
     </row>
-    <row r="55" spans="1:17" s="5" customFormat="1">
+    <row r="55" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A55" s="6">
         <v>43252</v>
       </c>
@@ -4080,7 +4088,7 @@
         <v>-2.66</v>
       </c>
     </row>
-    <row r="56" spans="1:17" s="5" customFormat="1">
+    <row r="56" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A56" s="6">
         <v>43221</v>
       </c>
@@ -4133,7 +4141,7 @@
         <v>-3.6</v>
       </c>
     </row>
-    <row r="57" spans="1:17" s="5" customFormat="1">
+    <row r="57" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A57" s="6">
         <v>43191</v>
       </c>
@@ -4186,7 +4194,7 @@
         <v>-7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="58" spans="1:17" s="5" customFormat="1">
+    <row r="58" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A58" s="6">
         <v>43160</v>
       </c>
@@ -4239,7 +4247,7 @@
         <v>-3.79</v>
       </c>
     </row>
-    <row r="59" spans="1:17" s="5" customFormat="1">
+    <row r="59" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A59" s="6">
         <v>43132</v>
       </c>
@@ -4292,7 +4300,7 @@
         <v>-5.78</v>
       </c>
     </row>
-    <row r="60" spans="1:17" s="5" customFormat="1">
+    <row r="60" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A60" s="6">
         <v>43101</v>
       </c>
@@ -4345,7 +4353,7 @@
         <v>25.4</v>
       </c>
     </row>
-    <row r="61" spans="1:17" s="5" customFormat="1">
+    <row r="61" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A61" s="6">
         <v>43070</v>
       </c>
@@ -4398,7 +4406,7 @@
         <v>-12.2</v>
       </c>
     </row>
-    <row r="62" spans="1:17" s="5" customFormat="1">
+    <row r="62" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A62" s="6">
         <v>43040</v>
       </c>
@@ -4451,7 +4459,7 @@
         <v>-14.2</v>
       </c>
     </row>
-    <row r="63" spans="1:17" s="5" customFormat="1">
+    <row r="63" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A63" s="6">
         <v>43009</v>
       </c>
@@ -4504,7 +4512,7 @@
         <v>-15.7</v>
       </c>
     </row>
-    <row r="64" spans="1:17" s="5" customFormat="1">
+    <row r="64" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A64" s="6">
         <v>42979</v>
       </c>
@@ -4557,7 +4565,7 @@
         <v>-16.8</v>
       </c>
     </row>
-    <row r="65" spans="1:17" s="5" customFormat="1">
+    <row r="65" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A65" s="6">
         <v>42948</v>
       </c>
@@ -4610,7 +4618,7 @@
         <v>-16.899999999999999</v>
       </c>
     </row>
-    <row r="66" spans="1:17" s="5" customFormat="1">
+    <row r="66" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A66" s="6">
         <v>42917</v>
       </c>
@@ -4663,7 +4671,7 @@
         <v>-17.2</v>
       </c>
     </row>
-    <row r="67" spans="1:17" s="5" customFormat="1">
+    <row r="67" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A67" s="6">
         <v>42887</v>
       </c>
@@ -4716,7 +4724,7 @@
         <v>-17</v>
       </c>
     </row>
-    <row r="68" spans="1:17" s="5" customFormat="1">
+    <row r="68" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A68" s="6">
         <v>42856</v>
       </c>
@@ -4769,7 +4777,7 @@
         <v>-18.3</v>
       </c>
     </row>
-    <row r="69" spans="1:17" s="5" customFormat="1">
+    <row r="69" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A69" s="6">
         <v>42826</v>
       </c>
@@ -4822,7 +4830,7 @@
         <v>-23.5</v>
       </c>
     </row>
-    <row r="70" spans="1:17" s="5" customFormat="1">
+    <row r="70" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A70" s="6">
         <v>42795</v>
       </c>
@@ -4875,7 +4883,7 @@
         <v>-21.7</v>
       </c>
     </row>
-    <row r="71" spans="1:17" s="5" customFormat="1">
+    <row r="71" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A71" s="6">
         <v>42767</v>
       </c>
@@ -4928,7 +4936,7 @@
         <v>-23</v>
       </c>
     </row>
-    <row r="72" spans="1:17" s="5" customFormat="1">
+    <row r="72" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A72" s="6">
         <v>42736</v>
       </c>
@@ -4981,7 +4989,7 @@
         <v>-44.6</v>
       </c>
     </row>
-    <row r="73" spans="1:17" s="5" customFormat="1">
+    <row r="73" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A73" s="6">
         <v>42705</v>
       </c>
@@ -5034,7 +5042,7 @@
         <v>-4.0599999999999996</v>
       </c>
     </row>
-    <row r="74" spans="1:17" s="5" customFormat="1">
+    <row r="74" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A74" s="6">
         <v>42675</v>
       </c>
@@ -5087,7 +5095,7 @@
         <v>-2.4</v>
       </c>
     </row>
-    <row r="75" spans="1:17" s="5" customFormat="1">
+    <row r="75" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A75" s="6">
         <v>42644</v>
       </c>
@@ -5140,7 +5148,7 @@
         <v>-1.66</v>
       </c>
     </row>
-    <row r="76" spans="1:17" s="5" customFormat="1">
+    <row r="76" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A76" s="6">
         <v>42614</v>
       </c>
@@ -5193,7 +5201,7 @@
         <v>-0.35</v>
       </c>
     </row>
-    <row r="77" spans="1:17" s="5" customFormat="1">
+    <row r="77" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A77" s="6">
         <v>42583</v>
       </c>
@@ -5246,7 +5254,7 @@
         <v>0.55000000000000004</v>
       </c>
     </row>
-    <row r="78" spans="1:17" s="5" customFormat="1">
+    <row r="78" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A78" s="6">
         <v>42552</v>
       </c>
@@ -5299,7 +5307,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:17" s="5" customFormat="1">
+    <row r="79" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A79" s="6">
         <v>42522</v>
       </c>
@@ -5352,7 +5360,7 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="80" spans="1:17" s="5" customFormat="1">
+    <row r="80" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A80" s="6">
         <v>42491</v>
       </c>
@@ -5405,7 +5413,7 @@
         <v>2.96</v>
       </c>
     </row>
-    <row r="81" spans="1:17" s="5" customFormat="1">
+    <row r="81" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A81" s="6">
         <v>42461</v>
       </c>
@@ -5458,7 +5466,7 @@
         <v>9.7200000000000006</v>
       </c>
     </row>
-    <row r="82" spans="1:17" s="5" customFormat="1">
+    <row r="82" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A82" s="6">
         <v>42430</v>
       </c>
@@ -5511,7 +5519,7 @@
         <v>16.7</v>
       </c>
     </row>
-    <row r="83" spans="1:17" s="5" customFormat="1">
+    <row r="83" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A83" s="6">
         <v>42401</v>
       </c>
@@ -5564,7 +5572,7 @@
         <v>7.84</v>
       </c>
     </row>
-    <row r="84" spans="1:17" s="5" customFormat="1">
+    <row r="84" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A84" s="6">
         <v>42370</v>
       </c>
@@ -5617,7 +5625,7 @@
         <v>-0.52</v>
       </c>
     </row>
-    <row r="85" spans="1:17" s="5" customFormat="1">
+    <row r="85" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A85" s="6">
         <v>42339</v>
       </c>
@@ -5670,7 +5678,7 @@
         <v>3.27</v>
       </c>
     </row>
-    <row r="86" spans="1:17" s="5" customFormat="1">
+    <row r="86" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A86" s="6">
         <v>42309</v>
       </c>
@@ -5723,7 +5731,7 @@
         <v>3.43</v>
       </c>
     </row>
-    <row r="87" spans="1:17" s="5" customFormat="1">
+    <row r="87" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A87" s="6">
         <v>42278</v>
       </c>
@@ -5776,7 +5784,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="88" spans="1:17" s="5" customFormat="1">
+    <row r="88" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A88" s="6">
         <v>42248</v>
       </c>
@@ -5829,7 +5837,7 @@
         <v>2.74</v>
       </c>
     </row>
-    <row r="89" spans="1:17" s="5" customFormat="1">
+    <row r="89" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A89" s="6">
         <v>42217</v>
       </c>
@@ -5882,7 +5890,7 @@
         <v>2.15</v>
       </c>
     </row>
-    <row r="90" spans="1:17" s="5" customFormat="1">
+    <row r="90" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A90" s="6">
         <v>42186</v>
       </c>
@@ -5935,7 +5943,7 @@
         <v>-0.3</v>
       </c>
     </row>
-    <row r="91" spans="1:17" s="5" customFormat="1">
+    <row r="91" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A91" s="6">
         <v>42156</v>
       </c>
@@ -5988,7 +5996,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="92" spans="1:17" s="5" customFormat="1">
+    <row r="92" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A92" s="6">
         <v>42125</v>
       </c>
@@ -6041,7 +6049,7 @@
         <v>-1.5</v>
       </c>
     </row>
-    <row r="93" spans="1:17" s="5" customFormat="1">
+    <row r="93" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A93" s="6">
         <v>42095</v>
       </c>
@@ -6094,7 +6102,7 @@
         <v>-4.33</v>
       </c>
     </row>
-    <row r="94" spans="1:17" s="5" customFormat="1">
+    <row r="94" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A94" s="6">
         <v>42064</v>
       </c>
@@ -6147,7 +6155,7 @@
         <v>-9.16</v>
       </c>
     </row>
-    <row r="95" spans="1:17" s="5" customFormat="1">
+    <row r="95" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A95" s="6">
         <v>42036</v>
       </c>
@@ -6200,7 +6208,7 @@
         <v>-11.6</v>
       </c>
     </row>
-    <row r="96" spans="1:17" s="5" customFormat="1">
+    <row r="96" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A96" s="6">
         <v>42005</v>
       </c>
@@ -6253,7 +6261,7 @@
         <v>24.7</v>
       </c>
     </row>
-    <row r="97" spans="1:17" s="5" customFormat="1">
+    <row r="97" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A97" s="6">
         <v>41974</v>
       </c>
@@ -6306,7 +6314,7 @@
         <v>-2.31</v>
       </c>
     </row>
-    <row r="98" spans="1:17" s="5" customFormat="1">
+    <row r="98" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A98" s="6">
         <v>41944</v>
       </c>
@@ -6359,7 +6367,7 @@
         <v>-3.29</v>
       </c>
     </row>
-    <row r="99" spans="1:17" s="5" customFormat="1">
+    <row r="99" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A99" s="6">
         <v>41913</v>
       </c>
@@ -6412,7 +6420,7 @@
         <v>-3.94</v>
       </c>
     </row>
-    <row r="100" spans="1:17" s="5" customFormat="1">
+    <row r="100" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A100" s="6">
         <v>41883</v>
       </c>
@@ -6465,7 +6473,7 @@
         <v>-2.73</v>
       </c>
     </row>
-    <row r="101" spans="1:17" s="5" customFormat="1">
+    <row r="101" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A101" s="6">
         <v>41852</v>
       </c>
@@ -6518,7 +6526,7 @@
         <v>-1.83</v>
       </c>
     </row>
-    <row r="102" spans="1:17" s="5" customFormat="1">
+    <row r="102" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A102" s="6">
         <v>41821</v>
       </c>
@@ -6571,7 +6579,7 @@
         <v>-0.39</v>
       </c>
     </row>
-    <row r="103" spans="1:17" s="5" customFormat="1">
+    <row r="103" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A103" s="6">
         <v>41791</v>
       </c>
@@ -6624,7 +6632,7 @@
         <v>1.46</v>
       </c>
     </row>
-    <row r="104" spans="1:17" s="5" customFormat="1">
+    <row r="104" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A104" s="6">
         <v>41760</v>
       </c>
@@ -6677,7 +6685,7 @@
         <v>5.94</v>
       </c>
     </row>
-    <row r="105" spans="1:17" s="5" customFormat="1">
+    <row r="105" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A105" s="6">
         <v>41730</v>
       </c>
@@ -6730,7 +6738,7 @@
         <v>17.8</v>
       </c>
     </row>
-    <row r="106" spans="1:17" s="5" customFormat="1">
+    <row r="106" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A106" s="6">
         <v>41699</v>
       </c>
@@ -6783,7 +6791,7 @@
         <v>30.8</v>
       </c>
     </row>
-    <row r="107" spans="1:17" s="5" customFormat="1">
+    <row r="107" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A107" s="6">
         <v>41671</v>
       </c>
@@ -6836,7 +6844,7 @@
         <v>35.9</v>
       </c>
     </row>
-    <row r="108" spans="1:17" s="5" customFormat="1">
+    <row r="108" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A108" s="6">
         <v>41640</v>
       </c>
@@ -6889,7 +6897,7 @@
         <v>-8.06</v>
       </c>
     </row>
-    <row r="109" spans="1:17" s="5" customFormat="1">
+    <row r="109" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A109" s="6">
         <v>41609</v>
       </c>
@@ -6942,7 +6950,7 @@
         <v>12.9</v>
       </c>
     </row>
-    <row r="110" spans="1:17" s="5" customFormat="1">
+    <row r="110" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A110" s="6">
         <v>41579</v>
       </c>
@@ -6995,7 +7003,7 @@
         <v>13.9</v>
       </c>
     </row>
-    <row r="111" spans="1:17" s="5" customFormat="1">
+    <row r="111" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A111" s="6">
         <v>41548</v>
       </c>
@@ -7048,7 +7056,7 @@
         <v>15.8</v>
       </c>
     </row>
-    <row r="112" spans="1:17" s="5" customFormat="1">
+    <row r="112" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A112" s="6">
         <v>41518</v>
       </c>
@@ -7101,7 +7109,7 @@
         <v>17.399999999999999</v>
       </c>
     </row>
-    <row r="113" spans="1:17" s="5" customFormat="1">
+    <row r="113" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A113" s="6">
         <v>41487</v>
       </c>
@@ -7154,7 +7162,7 @@
         <v>16.7</v>
       </c>
     </row>
-    <row r="114" spans="1:17" s="5" customFormat="1">
+    <row r="114" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A114" s="6">
         <v>41456</v>
       </c>
@@ -7207,7 +7215,7 @@
         <v>19.5</v>
       </c>
     </row>
-    <row r="115" spans="1:17" s="5" customFormat="1">
+    <row r="115" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A115" s="6">
         <v>41426</v>
       </c>
@@ -7260,7 +7268,7 @@
         <v>21.7</v>
       </c>
     </row>
-    <row r="116" spans="1:17" s="5" customFormat="1">
+    <row r="116" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A116" s="6">
         <v>41395</v>
       </c>
@@ -7313,7 +7321,7 @@
         <v>19.3</v>
       </c>
     </row>
-    <row r="117" spans="1:17" s="5" customFormat="1">
+    <row r="117" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A117" s="6">
         <v>41365</v>
       </c>
@@ -7366,7 +7374,7 @@
         <v>14.1</v>
       </c>
     </row>
-    <row r="118" spans="1:17" s="5" customFormat="1">
+    <row r="118" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A118" s="6">
         <v>41334</v>
       </c>
@@ -7419,7 +7427,7 @@
         <v>1.82</v>
       </c>
     </row>
-    <row r="119" spans="1:17" s="5" customFormat="1">
+    <row r="119" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A119" s="6">
         <v>41306</v>
       </c>
@@ -7472,7 +7480,7 @@
         <v>-0.77</v>
       </c>
     </row>
-    <row r="120" spans="1:17" s="5" customFormat="1">
+    <row r="120" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A120" s="6">
         <v>41275</v>
       </c>
@@ -7525,7 +7533,7 @@
         <v>36.9</v>
       </c>
     </row>
-    <row r="121" spans="1:17" s="5" customFormat="1">
+    <row r="121" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A121" s="6">
         <v>41244</v>
       </c>
@@ -7578,7 +7586,7 @@
         <v>9.42</v>
       </c>
     </row>
-    <row r="122" spans="1:17" s="5" customFormat="1">
+    <row r="122" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A122" s="6">
         <v>41214</v>
       </c>
@@ -7631,7 +7639,7 @@
         <v>9.14</v>
       </c>
     </row>
-    <row r="123" spans="1:17" s="5" customFormat="1">
+    <row r="123" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A123" s="6">
         <v>41183</v>
       </c>
@@ -7684,7 +7692,7 @@
         <v>8.81</v>
       </c>
     </row>
-    <row r="124" spans="1:17" s="5" customFormat="1">
+    <row r="124" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A124" s="6">
         <v>41153</v>
       </c>
@@ -7737,7 +7745,7 @@
         <v>8.24</v>
       </c>
     </row>
-    <row r="125" spans="1:17" s="5" customFormat="1">
+    <row r="125" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A125" s="6">
         <v>41122</v>
       </c>
@@ -7790,7 +7798,7 @@
         <v>6.85</v>
       </c>
     </row>
-    <row r="126" spans="1:17" s="5" customFormat="1">
+    <row r="126" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A126" s="6">
         <v>41091</v>
       </c>
@@ -7843,7 +7851,7 @@
         <v>5.66</v>
       </c>
     </row>
-    <row r="127" spans="1:17" s="5" customFormat="1">
+    <row r="127" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A127" s="6">
         <v>41061</v>
       </c>
@@ -7896,7 +7904,7 @@
         <v>4.4000000000000004</v>
       </c>
     </row>
-    <row r="128" spans="1:17" s="5" customFormat="1">
+    <row r="128" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A128" s="6">
         <v>41030</v>
       </c>
@@ -7949,7 +7957,7 @@
         <v>1.54</v>
       </c>
     </row>
-    <row r="129" spans="1:17" s="5" customFormat="1">
+    <row r="129" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A129" s="6">
         <v>41000</v>
       </c>
@@ -8002,7 +8010,7 @@
         <v>-6.93</v>
       </c>
     </row>
-    <row r="130" spans="1:17" s="5" customFormat="1">
+    <row r="130" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A130" s="6">
         <v>40969</v>
       </c>
@@ -8055,7 +8063,7 @@
         <v>-6.91</v>
       </c>
     </row>
-    <row r="131" spans="1:17" s="5" customFormat="1">
+    <row r="131" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A131" s="6">
         <v>40940</v>
       </c>
@@ -8108,7 +8116,7 @@
         <v>-2.41</v>
       </c>
     </row>
-    <row r="132" spans="1:17" s="5" customFormat="1">
+    <row r="132" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A132" s="6">
         <v>40909</v>
       </c>
@@ -8161,7 +8169,7 @@
         <v>-10.6</v>
       </c>
     </row>
-    <row r="133" spans="1:17" s="5" customFormat="1">
+    <row r="133" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A133" s="6">
         <v>40878</v>
       </c>
@@ -8214,7 +8222,7 @@
         <v>-11.3</v>
       </c>
     </row>
-    <row r="134" spans="1:17" s="5" customFormat="1">
+    <row r="134" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A134" s="6">
         <v>40848</v>
       </c>
@@ -8267,7 +8275,7 @@
         <v>-11.2</v>
       </c>
     </row>
-    <row r="135" spans="1:17" s="5" customFormat="1">
+    <row r="135" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A135" s="6">
         <v>40817</v>
       </c>
@@ -8320,7 +8328,7 @@
         <v>-9.7799999999999994</v>
       </c>
     </row>
-    <row r="136" spans="1:17" s="5" customFormat="1">
+    <row r="136" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A136" s="6">
         <v>40787</v>
       </c>
@@ -8373,7 +8381,7 @@
         <v>-10.8</v>
       </c>
     </row>
-    <row r="137" spans="1:17" s="5" customFormat="1">
+    <row r="137" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A137" s="6">
         <v>40756</v>
       </c>
@@ -8426,7 +8434,7 @@
         <v>-11.2</v>
       </c>
     </row>
-    <row r="138" spans="1:17" s="5" customFormat="1">
+    <row r="138" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A138" s="6">
         <v>40725</v>
       </c>
@@ -8479,7 +8487,7 @@
         <v>-9.08</v>
       </c>
     </row>
-    <row r="139" spans="1:17" s="5" customFormat="1">
+    <row r="139" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A139" s="6">
         <v>40695</v>
       </c>
@@ -8532,7 +8540,7 @@
         <v>-8.35</v>
       </c>
     </row>
-    <row r="140" spans="1:17" s="5" customFormat="1">
+    <row r="140" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A140" s="6">
         <v>40664</v>
       </c>
@@ -8585,7 +8593,7 @@
         <v>-4.21</v>
       </c>
     </row>
-    <row r="141" spans="1:17" s="5" customFormat="1">
+    <row r="141" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A141" s="6">
         <v>40634</v>
       </c>
@@ -8638,7 +8646,7 @@
         <v>-0.67</v>
       </c>
     </row>
-    <row r="142" spans="1:17" s="5" customFormat="1">
+    <row r="142" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A142" s="6">
         <v>40603</v>
       </c>
@@ -8691,7 +8699,7 @@
         <v>9.57</v>
       </c>
     </row>
-    <row r="143" spans="1:17" s="5" customFormat="1">
+    <row r="143" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A143" s="6">
         <v>40575</v>
       </c>
@@ -8744,7 +8752,7 @@
         <v>-5.46</v>
       </c>
     </row>
-    <row r="144" spans="1:17" s="5" customFormat="1">
+    <row r="144" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A144" s="6">
         <v>40544</v>
       </c>
@@ -8797,7 +8805,7 @@
         <v>-14</v>
       </c>
     </row>
-    <row r="145" spans="1:17" s="5" customFormat="1">
+    <row r="145" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A145" s="6">
         <v>40513</v>
       </c>
@@ -8850,7 +8858,7 @@
         <v>-3.57</v>
       </c>
     </row>
-    <row r="146" spans="1:17" s="5" customFormat="1">
+    <row r="146" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A146" s="6">
         <v>40483</v>
       </c>
@@ -8903,7 +8911,7 @@
         <v>1.96</v>
       </c>
     </row>
-    <row r="147" spans="1:17" s="5" customFormat="1">
+    <row r="147" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A147" s="6">
         <v>40452</v>
       </c>
@@ -8956,7 +8964,7 @@
         <v>1.65</v>
       </c>
     </row>
-    <row r="148" spans="1:17" s="5" customFormat="1">
+    <row r="148" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A148" s="6">
         <v>40422</v>
       </c>
@@ -9009,7 +9017,7 @@
         <v>2.7</v>
       </c>
     </row>
-    <row r="149" spans="1:17" s="5" customFormat="1">
+    <row r="149" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A149" s="6">
         <v>40391</v>
       </c>
@@ -9062,7 +9070,7 @@
         <v>3.91</v>
       </c>
     </row>
-    <row r="150" spans="1:17" s="5" customFormat="1">
+    <row r="150" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A150" s="6">
         <v>40360</v>
       </c>
@@ -9115,7 +9123,7 @@
         <v>8.5500000000000007</v>
       </c>
     </row>
-    <row r="151" spans="1:17" s="5" customFormat="1">
+    <row r="151" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A151" s="6">
         <v>40330</v>
       </c>
@@ -9168,7 +9176,7 @@
         <v>9.7799999999999994</v>
       </c>
     </row>
-    <row r="152" spans="1:17" s="5" customFormat="1">
+    <row r="152" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A152" s="6">
         <v>40299</v>
       </c>
@@ -9221,7 +9229,7 @@
         <v>13.7</v>
       </c>
     </row>
-    <row r="153" spans="1:17" s="5" customFormat="1">
+    <row r="153" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A153" s="6">
         <v>40269</v>
       </c>
@@ -9274,7 +9282,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="154" spans="1:17" s="5" customFormat="1">
+    <row r="154" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A154" s="6">
         <v>40238</v>
       </c>
@@ -9327,7 +9335,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="155" spans="1:17" s="5" customFormat="1">
+    <row r="155" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A155" s="6">
         <v>40210</v>
       </c>
@@ -9380,7 +9388,7 @@
         <v>26.9</v>
       </c>
     </row>
-    <row r="156" spans="1:17" s="5" customFormat="1">
+    <row r="156" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A156" s="6">
         <v>40179</v>
       </c>
@@ -9433,7 +9441,7 @@
         <v>99.9</v>
       </c>
     </row>
-    <row r="157" spans="1:17" s="5" customFormat="1">
+    <row r="157" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A157" s="6">
         <v>40148</v>
       </c>
@@ -9486,7 +9494,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="158" spans="1:17" s="5" customFormat="1">
+    <row r="158" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A158" s="6">
         <v>40118</v>
       </c>
@@ -9539,7 +9547,7 @@
         <v>2.63</v>
       </c>
     </row>
-    <row r="159" spans="1:17" s="5" customFormat="1">
+    <row r="159" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A159" s="6">
         <v>40087</v>
       </c>
@@ -9592,7 +9600,7 @@
         <v>2.75</v>
       </c>
     </row>
-    <row r="160" spans="1:17" s="5" customFormat="1">
+    <row r="160" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A160" s="6">
         <v>40057</v>
       </c>
@@ -9645,7 +9653,7 @@
         <v>9.6</v>
       </c>
     </row>
-    <row r="161" spans="1:17" s="5" customFormat="1">
+    <row r="161" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A161" s="6">
         <v>40026</v>
       </c>
@@ -9698,7 +9706,7 @@
         <v>9.23</v>
       </c>
     </row>
-    <row r="162" spans="1:17" s="5" customFormat="1">
+    <row r="162" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A162" s="6">
         <v>39995</v>
       </c>
@@ -9751,7 +9759,7 @@
         <v>4.97</v>
       </c>
     </row>
-    <row r="163" spans="1:17" s="5" customFormat="1">
+    <row r="163" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A163" s="6">
         <v>39965</v>
       </c>
@@ -9804,7 +9812,7 @@
         <v>13.2</v>
       </c>
     </row>
-    <row r="164" spans="1:17" s="5" customFormat="1">
+    <row r="164" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A164" s="6">
         <v>39934</v>
       </c>
@@ -9857,7 +9865,7 @@
         <v>8.1</v>
       </c>
     </row>
-    <row r="165" spans="1:17" s="5" customFormat="1">
+    <row r="165" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A165" s="6">
         <v>39904</v>
       </c>
@@ -9910,7 +9918,7 @@
         <v>6.07</v>
       </c>
     </row>
-    <row r="166" spans="1:17" s="5" customFormat="1">
+    <row r="166" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A166" s="6">
         <v>39873</v>
       </c>
@@ -9963,7 +9971,7 @@
         <v>4.1900000000000004</v>
       </c>
     </row>
-    <row r="167" spans="1:17" s="5" customFormat="1">
+    <row r="167" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A167" s="6">
         <v>39845</v>
       </c>
@@ -10016,7 +10024,7 @@
         <v>9.1</v>
       </c>
     </row>
-    <row r="168" spans="1:17" s="5" customFormat="1">
+    <row r="168" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A168" s="6">
         <v>39814</v>
       </c>
@@ -10069,7 +10077,7 @@
         <v>-27.3</v>
       </c>
     </row>
-    <row r="169" spans="1:17" s="5" customFormat="1">
+    <row r="169" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A169" s="6">
         <v>39783</v>
       </c>
@@ -10122,7 +10130,7 @@
         <v>8.09</v>
       </c>
     </row>
-    <row r="170" spans="1:17" s="5" customFormat="1">
+    <row r="170" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A170" s="6">
         <v>39753</v>
       </c>
@@ -10175,7 +10183,7 @@
         <v>10.3</v>
       </c>
     </row>
-    <row r="171" spans="1:17" s="5" customFormat="1">
+    <row r="171" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A171" s="6">
         <v>39722</v>
       </c>
@@ -10228,7 +10236,7 @@
         <v>10.6</v>
       </c>
     </row>
-    <row r="172" spans="1:17" s="5" customFormat="1">
+    <row r="172" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A172" s="6">
         <v>39692</v>
       </c>
@@ -10281,7 +10289,7 @@
         <v>4.74</v>
       </c>
     </row>
-    <row r="173" spans="1:17" s="5" customFormat="1">
+    <row r="173" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A173" s="6">
         <v>39661</v>
       </c>
@@ -10334,7 +10342,7 @@
         <v>5.53</v>
       </c>
     </row>
-    <row r="174" spans="1:17" s="5" customFormat="1">
+    <row r="174" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A174" s="6">
         <v>39630</v>
       </c>
@@ -10387,7 +10395,7 @@
         <v>5.09</v>
       </c>
     </row>
-    <row r="175" spans="1:17" s="5" customFormat="1">
+    <row r="175" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A175" s="6">
         <v>39600</v>
       </c>
@@ -10440,7 +10448,7 @@
         <v>-6.34</v>
       </c>
     </row>
-    <row r="176" spans="1:17" s="5" customFormat="1">
+    <row r="176" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A176" s="6">
         <v>39569</v>
       </c>
@@ -10493,7 +10501,7 @@
         <v>-6.61</v>
       </c>
     </row>
-    <row r="177" spans="1:17" s="5" customFormat="1">
+    <row r="177" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A177" s="6">
         <v>39539</v>
       </c>
@@ -10546,7 +10554,7 @@
         <v>-6.29</v>
       </c>
     </row>
-    <row r="178" spans="1:17" s="5" customFormat="1">
+    <row r="178" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A178" s="6">
         <v>39508</v>
       </c>
@@ -10599,7 +10607,7 @@
         <v>-5.73</v>
       </c>
     </row>
-    <row r="179" spans="1:17" s="5" customFormat="1">
+    <row r="179" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A179" s="6">
         <v>39479</v>
       </c>
@@ -10652,7 +10660,7 @@
         <v>-9.3000000000000007</v>
       </c>
     </row>
-    <row r="180" spans="1:17" s="5" customFormat="1">
+    <row r="180" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A180" s="6">
         <v>39448</v>
       </c>
@@ -10705,7 +10713,7 @@
         <v>-13</v>
       </c>
     </row>
-    <row r="181" spans="1:17" s="5" customFormat="1">
+    <row r="181" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A181" s="6">
         <v>39417</v>
       </c>
@@ -10758,7 +10766,7 @@
         <v>4.88</v>
       </c>
     </row>
-    <row r="182" spans="1:17" s="5" customFormat="1">
+    <row r="182" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A182" s="6">
         <v>39387</v>
       </c>
@@ -10811,7 +10819,7 @@
         <v>6.33</v>
       </c>
     </row>
-    <row r="183" spans="1:17" s="5" customFormat="1">
+    <row r="183" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A183" s="6">
         <v>39356</v>
       </c>
@@ -10864,7 +10872,7 @@
         <v>7.07</v>
       </c>
     </row>
-    <row r="184" spans="1:17" s="5" customFormat="1">
+    <row r="184" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A184" s="6">
         <v>39326</v>
       </c>
@@ -10917,7 +10925,7 @@
         <v>7.67</v>
       </c>
     </row>
-    <row r="185" spans="1:17" s="5" customFormat="1">
+    <row r="185" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A185" s="6">
         <v>39295</v>
       </c>
@@ -10970,7 +10978,7 @@
         <v>6.43</v>
       </c>
     </row>
-    <row r="186" spans="1:17" s="5" customFormat="1">
+    <row r="186" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A186" s="6">
         <v>39264</v>
       </c>
@@ -11023,7 +11031,7 @@
         <v>7.78</v>
       </c>
     </row>
-    <row r="187" spans="1:17" s="5" customFormat="1">
+    <row r="187" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A187" s="6">
         <v>39234</v>
       </c>
@@ -11076,7 +11084,7 @@
         <v>9.32</v>
       </c>
     </row>
-    <row r="188" spans="1:17" s="5" customFormat="1">
+    <row r="188" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A188" s="6">
         <v>39203</v>
       </c>
@@ -11129,7 +11137,7 @@
         <v>13.8</v>
       </c>
     </row>
-    <row r="189" spans="1:17" s="5" customFormat="1">
+    <row r="189" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A189" s="6">
         <v>39173</v>
       </c>
@@ -11182,7 +11190,7 @@
         <v>18.7</v>
       </c>
     </row>
-    <row r="190" spans="1:17" s="5" customFormat="1">
+    <row r="190" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A190" s="6">
         <v>39142</v>
       </c>
@@ -11235,7 +11243,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="191" spans="1:17" s="5" customFormat="1">
+    <row r="191" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A191" s="6">
         <v>39114</v>
       </c>
@@ -11288,7 +11296,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="192" spans="1:17" s="5" customFormat="1">
+    <row r="192" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A192" s="6">
         <v>39083</v>
       </c>
@@ -11341,7 +11349,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="193" spans="1:17" s="5" customFormat="1">
+    <row r="193" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A193" s="6">
         <v>39052</v>
       </c>
@@ -11394,7 +11402,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="194" spans="1:17" s="5" customFormat="1">
+    <row r="194" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A194" s="6">
         <v>39022</v>
       </c>
@@ -11447,7 +11455,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="195" spans="1:17" s="5" customFormat="1">
+    <row r="195" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A195" s="6">
         <v>38991</v>
       </c>
@@ -11500,7 +11508,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="196" spans="1:17" s="5" customFormat="1">
+    <row r="196" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A196" s="6">
         <v>38961</v>
       </c>
@@ -11553,7 +11561,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="197" spans="1:17" s="5" customFormat="1">
+    <row r="197" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A197" s="6">
         <v>38930</v>
       </c>
@@ -11606,7 +11614,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="198" spans="1:17" s="5" customFormat="1">
+    <row r="198" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A198" s="6">
         <v>38899</v>
       </c>
@@ -11659,7 +11667,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="199" spans="1:17" s="5" customFormat="1">
+    <row r="199" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A199" s="6">
         <v>38869</v>
       </c>
@@ -11712,7 +11720,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="200" spans="1:17" s="5" customFormat="1">
+    <row r="200" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A200" s="6">
         <v>38838</v>
       </c>
@@ -11765,7 +11773,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="201" spans="1:17" s="5" customFormat="1">
+    <row r="201" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A201" s="6">
         <v>38808</v>
       </c>
@@ -11818,7 +11826,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="202" spans="1:17" s="5" customFormat="1">
+    <row r="202" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A202" s="6">
         <v>38777</v>
       </c>
@@ -11871,7 +11879,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="203" spans="1:17" s="5" customFormat="1">
+    <row r="203" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A203" s="6">
         <v>38749</v>
       </c>
@@ -11924,7 +11932,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="204" spans="1:17" s="5" customFormat="1">
+    <row r="204" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A204" s="6">
         <v>38718</v>
       </c>
@@ -11977,7 +11985,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="205" spans="1:17" s="5" customFormat="1">
+    <row r="205" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A205" s="6">
         <v>38687</v>
       </c>
@@ -12030,7 +12038,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="206" spans="1:17" s="5" customFormat="1">
+    <row r="206" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A206" s="6">
         <v>38657</v>
       </c>
@@ -12083,7 +12091,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="207" spans="1:17" s="5" customFormat="1">
+    <row r="207" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A207" s="6">
         <v>38626</v>
       </c>
@@ -12136,7 +12144,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="208" spans="1:17" s="5" customFormat="1">
+    <row r="208" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A208" s="6">
         <v>38596</v>
       </c>
@@ -12189,7 +12197,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="209" spans="1:17" s="5" customFormat="1">
+    <row r="209" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A209" s="6">
         <v>38565</v>
       </c>
@@ -12242,7 +12250,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="210" spans="1:17" s="5" customFormat="1">
+    <row r="210" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A210" s="6">
         <v>38534</v>
       </c>
@@ -12295,7 +12303,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="211" spans="1:17" s="5" customFormat="1">
+    <row r="211" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A211" s="6">
         <v>38504</v>
       </c>
@@ -12348,7 +12356,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="212" spans="1:17" s="5" customFormat="1">
+    <row r="212" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A212" s="6">
         <v>38473</v>
       </c>
@@ -12401,7 +12409,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="213" spans="1:17" s="5" customFormat="1">
+    <row r="213" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A213" s="6">
         <v>38443</v>
       </c>
@@ -12454,7 +12462,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="214" spans="1:17" s="5" customFormat="1">
+    <row r="214" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A214" s="6">
         <v>38412</v>
       </c>
@@ -12507,7 +12515,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="215" spans="1:17" s="5" customFormat="1">
+    <row r="215" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A215" s="6">
         <v>38384</v>
       </c>
@@ -12560,7 +12568,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="216" spans="1:17" s="5" customFormat="1">
+    <row r="216" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A216" s="6">
         <v>38353</v>
       </c>
@@ -12613,7 +12621,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="217" spans="1:17" s="5" customFormat="1">
+    <row r="217" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A217" s="6">
         <v>38322</v>
       </c>
@@ -12666,7 +12674,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="218" spans="1:17" s="5" customFormat="1">
+    <row r="218" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A218" s="6">
         <v>38292</v>
       </c>
@@ -12719,7 +12727,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="219" spans="1:17" s="5" customFormat="1">
+    <row r="219" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A219" s="6">
         <v>38261</v>
       </c>
@@ -12772,7 +12780,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="220" spans="1:17" s="5" customFormat="1">
+    <row r="220" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A220" s="6">
         <v>38231</v>
       </c>
@@ -12825,7 +12833,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="221" spans="1:17" s="5" customFormat="1">
+    <row r="221" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A221" s="6">
         <v>38200</v>
       </c>
@@ -12878,7 +12886,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="222" spans="1:17" s="5" customFormat="1">
+    <row r="222" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A222" s="6">
         <v>38169</v>
       </c>
@@ -12931,7 +12939,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="223" spans="1:17" s="5" customFormat="1">
+    <row r="223" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A223" s="6">
         <v>38139</v>
       </c>
@@ -12984,7 +12992,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="224" spans="1:17" s="5" customFormat="1">
+    <row r="224" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A224" s="6">
         <v>38108</v>
       </c>
@@ -13037,7 +13045,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="225" spans="1:17" s="5" customFormat="1">
+    <row r="225" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A225" s="6">
         <v>38078</v>
       </c>
@@ -13090,7 +13098,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="226" spans="1:17" s="5" customFormat="1">
+    <row r="226" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A226" s="6">
         <v>38047</v>
       </c>
@@ -13143,7 +13151,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="227" spans="1:17" s="5" customFormat="1">
+    <row r="227" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A227" s="6">
         <v>38018</v>
       </c>
@@ -13196,7 +13204,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="228" spans="1:17" s="5" customFormat="1">
+    <row r="228" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A228" s="6">
         <v>37987</v>
       </c>
@@ -13249,7 +13257,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="229" spans="1:17" s="5" customFormat="1">
+    <row r="229" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A229" s="6">
         <v>37956</v>
       </c>
@@ -13302,7 +13310,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="230" spans="1:17" s="5" customFormat="1">
+    <row r="230" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A230" s="6">
         <v>37926</v>
       </c>
@@ -13355,7 +13363,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="231" spans="1:17" s="5" customFormat="1">
+    <row r="231" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A231" s="6">
         <v>37895</v>
       </c>
@@ -13408,7 +13416,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="232" spans="1:17" s="5" customFormat="1">
+    <row r="232" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A232" s="6">
         <v>37865</v>
       </c>
@@ -13461,7 +13469,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="233" spans="1:17" s="5" customFormat="1">
+    <row r="233" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A233" s="6">
         <v>37834</v>
       </c>
@@ -13514,7 +13522,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="234" spans="1:17" s="5" customFormat="1">
+    <row r="234" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A234" s="6">
         <v>37803</v>
       </c>
@@ -13567,7 +13575,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="235" spans="1:17" s="5" customFormat="1">
+    <row r="235" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A235" s="6">
         <v>37773</v>
       </c>
@@ -13620,7 +13628,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="236" spans="1:17" s="5" customFormat="1">
+    <row r="236" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A236" s="6">
         <v>37742</v>
       </c>
@@ -13673,7 +13681,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="237" spans="1:17" s="5" customFormat="1">
+    <row r="237" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A237" s="6">
         <v>37712</v>
       </c>
@@ -13726,7 +13734,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="238" spans="1:17" s="5" customFormat="1">
+    <row r="238" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A238" s="6">
         <v>37681</v>
       </c>
@@ -13779,7 +13787,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="239" spans="1:17" s="5" customFormat="1">
+    <row r="239" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A239" s="6">
         <v>37653</v>
       </c>
@@ -13832,7 +13840,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="240" spans="1:17" s="5" customFormat="1">
+    <row r="240" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A240" s="6">
         <v>37622</v>
       </c>
@@ -13885,7 +13893,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="241" spans="1:17" s="5" customFormat="1">
+    <row r="241" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A241" s="6">
         <v>37591</v>
       </c>
@@ -13938,7 +13946,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="242" spans="1:17" s="5" customFormat="1">
+    <row r="242" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A242" s="6">
         <v>37561</v>
       </c>
@@ -13991,7 +13999,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="243" spans="1:17" s="5" customFormat="1">
+    <row r="243" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A243" s="6">
         <v>37530</v>
       </c>
@@ -14044,7 +14052,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="244" spans="1:17" s="5" customFormat="1">
+    <row r="244" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A244" s="6">
         <v>37500</v>
       </c>
@@ -14097,7 +14105,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="245" spans="1:17" s="5" customFormat="1">
+    <row r="245" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A245" s="6">
         <v>37469</v>
       </c>
@@ -14150,7 +14158,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="246" spans="1:17" s="5" customFormat="1">
+    <row r="246" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A246" s="6">
         <v>37438</v>
       </c>
@@ -14203,7 +14211,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="247" spans="1:17" s="5" customFormat="1">
+    <row r="247" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A247" s="6">
         <v>37408</v>
       </c>
@@ -14256,7 +14264,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="248" spans="1:17" s="5" customFormat="1">
+    <row r="248" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A248" s="6">
         <v>37377</v>
       </c>
@@ -14309,7 +14317,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="249" spans="1:17" s="5" customFormat="1">
+    <row r="249" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A249" s="6">
         <v>37347</v>
       </c>
@@ -14362,7 +14370,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="250" spans="1:17" s="5" customFormat="1">
+    <row r="250" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A250" s="6">
         <v>37316</v>
       </c>
@@ -14415,7 +14423,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="251" spans="1:17" s="5" customFormat="1">
+    <row r="251" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A251" s="6">
         <v>37288</v>
       </c>
@@ -14468,7 +14476,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="252" spans="1:17" s="5" customFormat="1">
+    <row r="252" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A252" s="6">
         <v>37257</v>
       </c>
@@ -14521,7 +14529,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="253" spans="1:17" s="5" customFormat="1">
+    <row r="253" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A253" s="6">
         <v>37226</v>
       </c>
@@ -14574,7 +14582,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="254" spans="1:17" s="5" customFormat="1">
+    <row r="254" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A254" s="6">
         <v>37196</v>
       </c>
@@ -14627,7 +14635,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="255" spans="1:17" s="5" customFormat="1">
+    <row r="255" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A255" s="6">
         <v>37165</v>
       </c>
@@ -14680,7 +14688,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="256" spans="1:17" s="5" customFormat="1">
+    <row r="256" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A256" s="6">
         <v>37135</v>
       </c>
@@ -14733,7 +14741,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="257" spans="1:17" s="5" customFormat="1">
+    <row r="257" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A257" s="6">
         <v>37104</v>
       </c>
@@ -14786,7 +14794,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="258" spans="1:17" s="5" customFormat="1">
+    <row r="258" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A258" s="6">
         <v>37073</v>
       </c>
@@ -14839,7 +14847,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="259" spans="1:17" s="5" customFormat="1">
+    <row r="259" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A259" s="6">
         <v>37043</v>
       </c>
@@ -14892,7 +14900,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="260" spans="1:17" s="5" customFormat="1">
+    <row r="260" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A260" s="6">
         <v>37012</v>
       </c>
@@ -14945,7 +14953,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="261" spans="1:17" s="5" customFormat="1">
+    <row r="261" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A261" s="6">
         <v>36982</v>
       </c>
@@ -14998,7 +15006,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="262" spans="1:17" s="5" customFormat="1">
+    <row r="262" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A262" s="6">
         <v>36951</v>
       </c>
@@ -15051,7 +15059,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="263" spans="1:17" s="5" customFormat="1">
+    <row r="263" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A263" s="6">
         <v>36923</v>
       </c>
@@ -15104,7 +15112,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="264" spans="1:17" s="5" customFormat="1">
+    <row r="264" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A264" s="6">
         <v>36892</v>
       </c>
@@ -15157,7 +15165,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="265" spans="1:17" s="5" customFormat="1">
+    <row r="265" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A265" s="6">
         <v>36861</v>
       </c>
@@ -15210,7 +15218,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="266" spans="1:17" s="5" customFormat="1">
+    <row r="266" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A266" s="6">
         <v>36831</v>
       </c>
@@ -15263,7 +15271,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="267" spans="1:17" s="5" customFormat="1">
+    <row r="267" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A267" s="6">
         <v>36800</v>
       </c>
@@ -15316,7 +15324,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="268" spans="1:17" s="5" customFormat="1">
+    <row r="268" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A268" s="6">
         <v>36770</v>
       </c>
@@ -15369,7 +15377,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="269" spans="1:17" s="5" customFormat="1">
+    <row r="269" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A269" s="6">
         <v>36739</v>
       </c>
@@ -15422,7 +15430,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="270" spans="1:17" s="5" customFormat="1">
+    <row r="270" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A270" s="6">
         <v>36708</v>
       </c>
@@ -15475,7 +15483,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="271" spans="1:17" s="5" customFormat="1">
+    <row r="271" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A271" s="6">
         <v>36678</v>
       </c>
@@ -15528,7 +15536,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="272" spans="1:17" s="5" customFormat="1">
+    <row r="272" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A272" s="6">
         <v>36647</v>
       </c>
@@ -15581,7 +15589,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="273" spans="1:17" s="5" customFormat="1">
+    <row r="273" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A273" s="6">
         <v>36617</v>
       </c>
@@ -15634,7 +15642,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="274" spans="1:17" s="5" customFormat="1">
+    <row r="274" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A274" s="6">
         <v>36586</v>
       </c>
@@ -15687,7 +15695,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="275" spans="1:17" s="5" customFormat="1">
+    <row r="275" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A275" s="6">
         <v>36557</v>
       </c>
@@ -15740,7 +15748,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="276" spans="1:17" s="5" customFormat="1">
+    <row r="276" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A276" s="6">
         <v>36526</v>
       </c>
@@ -15793,7 +15801,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="277" spans="1:17" s="5" customFormat="1">
+    <row r="277" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A277" s="6">
         <v>36495</v>
       </c>
@@ -15846,7 +15854,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="278" spans="1:17" s="5" customFormat="1">
+    <row r="278" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A278" s="6">
         <v>36465</v>
       </c>
@@ -15899,7 +15907,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="279" spans="1:17" s="5" customFormat="1">
+    <row r="279" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A279" s="6">
         <v>36434</v>
       </c>
@@ -15952,7 +15960,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="280" spans="1:17" s="5" customFormat="1">
+    <row r="280" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A280" s="6">
         <v>36404</v>
       </c>
@@ -16005,7 +16013,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="281" spans="1:17" s="5" customFormat="1">
+    <row r="281" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A281" s="6">
         <v>36373</v>
       </c>
@@ -16058,7 +16066,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="282" spans="1:17" s="5" customFormat="1">
+    <row r="282" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A282" s="6">
         <v>36342</v>
       </c>
@@ -16111,7 +16119,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="283" spans="1:17" s="5" customFormat="1">
+    <row r="283" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A283" s="6">
         <v>36312</v>
       </c>
@@ -16164,7 +16172,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="284" spans="1:17" s="5" customFormat="1">
+    <row r="284" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A284" s="6">
         <v>36281</v>
       </c>
@@ -16217,7 +16225,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="285" spans="1:17" s="5" customFormat="1">
+    <row r="285" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A285" s="6">
         <v>36251</v>
       </c>
@@ -16270,7 +16278,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="286" spans="1:17" s="5" customFormat="1">
+    <row r="286" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A286" s="6">
         <v>36220</v>
       </c>
@@ -16323,7 +16331,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="287" spans="1:17" s="5" customFormat="1">
+    <row r="287" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A287" s="6">
         <v>36192</v>
       </c>
@@ -16376,7 +16384,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="288" spans="1:17" s="5" customFormat="1">
+    <row r="288" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A288" s="6">
         <v>36161</v>
       </c>
@@ -16429,7 +16437,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="289" spans="1:17" s="5" customFormat="1">
+    <row r="289" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A289" s="6">
         <v>36130</v>
       </c>
@@ -16482,7 +16490,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="290" spans="1:17" s="5" customFormat="1">
+    <row r="290" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A290" s="6">
         <v>36100</v>
       </c>
@@ -16535,7 +16543,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="291" spans="1:17" s="5" customFormat="1">
+    <row r="291" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A291" s="6">
         <v>36069</v>
       </c>
@@ -16588,7 +16596,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="292" spans="1:17" s="5" customFormat="1">
+    <row r="292" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A292" s="6">
         <v>36039</v>
       </c>
@@ -16641,7 +16649,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="293" spans="1:17" s="5" customFormat="1">
+    <row r="293" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A293" s="6">
         <v>36008</v>
       </c>
@@ -16694,7 +16702,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="294" spans="1:17" s="5" customFormat="1">
+    <row r="294" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A294" s="6">
         <v>35977</v>
       </c>
@@ -16747,7 +16755,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="295" spans="1:17" s="5" customFormat="1">
+    <row r="295" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A295" s="6">
         <v>35947</v>
       </c>
@@ -16800,7 +16808,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="296" spans="1:17" s="5" customFormat="1">
+    <row r="296" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A296" s="6">
         <v>35916</v>
       </c>
@@ -16853,7 +16861,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="297" spans="1:17" s="5" customFormat="1">
+    <row r="297" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A297" s="6">
         <v>35886</v>
       </c>
@@ -16906,7 +16914,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="298" spans="1:17" s="5" customFormat="1">
+    <row r="298" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A298" s="6">
         <v>35827</v>
       </c>
@@ -16959,7 +16967,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="299" spans="1:17" s="5" customFormat="1">
+    <row r="299" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A299" s="6">
         <v>35796</v>
       </c>
@@ -17027,7 +17035,7 @@
     <mergeCell ref="H2:J2"/>
     <mergeCell ref="K2:L2"/>
   </mergeCells>
-  <phoneticPr fontId="24" type="noConversion"/>
+  <phoneticPr fontId="25" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>